--- a/Shiny/Datos limpios/pricing_semanal_historico_cebada.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico_cebada.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M570"/>
+  <dimension ref="A1:M573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -24863,19 +24863,19 @@
         <v>45957</v>
       </c>
       <c r="D570">
-        <v>450</v>
+        <v>77480.75</v>
       </c>
       <c r="E570">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="F570">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="G570">
-        <v>450</v>
+        <v>78020.75</v>
       </c>
       <c r="H570">
-        <v>7500</v>
+        <v>24258.08</v>
       </c>
       <c r="I570">
         <v>0</v>
@@ -24884,12 +24884,141 @@
         <v>0</v>
       </c>
       <c r="K570">
-        <v>7500</v>
+        <v>24258.08</v>
       </c>
       <c r="L570">
-        <v>7950</v>
+        <v>102278.83</v>
       </c>
       <c r="M570" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571">
+        <v>2025</v>
+      </c>
+      <c r="B571">
+        <v>45</v>
+      </c>
+      <c r="C571" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D571">
+        <v>84801.07000000001</v>
+      </c>
+      <c r="E571">
+        <v>0</v>
+      </c>
+      <c r="F571">
+        <v>2000</v>
+      </c>
+      <c r="G571">
+        <v>82801.07000000001</v>
+      </c>
+      <c r="H571">
+        <v>41766.96</v>
+      </c>
+      <c r="I571">
+        <v>0</v>
+      </c>
+      <c r="J571">
+        <v>0</v>
+      </c>
+      <c r="K571">
+        <v>41766.96</v>
+      </c>
+      <c r="L571">
+        <v>124568.03</v>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572">
+        <v>2025</v>
+      </c>
+      <c r="B572">
+        <v>46</v>
+      </c>
+      <c r="C572" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D572">
+        <v>75783.97</v>
+      </c>
+      <c r="E572">
+        <v>2060</v>
+      </c>
+      <c r="F572">
+        <v>410</v>
+      </c>
+      <c r="G572">
+        <v>77433.97</v>
+      </c>
+      <c r="H572">
+        <v>270</v>
+      </c>
+      <c r="I572">
+        <v>0</v>
+      </c>
+      <c r="J572">
+        <v>0</v>
+      </c>
+      <c r="K572">
+        <v>270</v>
+      </c>
+      <c r="L572">
+        <v>77703.97</v>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <v>2025</v>
+      </c>
+      <c r="B573">
+        <v>47</v>
+      </c>
+      <c r="C573" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D573">
+        <v>107600.85</v>
+      </c>
+      <c r="E573">
+        <v>2200</v>
+      </c>
+      <c r="F573">
+        <v>1360</v>
+      </c>
+      <c r="G573">
+        <v>108440.85</v>
+      </c>
+      <c r="H573">
+        <v>17413</v>
+      </c>
+      <c r="I573">
+        <v>0</v>
+      </c>
+      <c r="J573">
+        <v>0</v>
+      </c>
+      <c r="K573">
+        <v>17413</v>
+      </c>
+      <c r="L573">
+        <v>125853.85</v>
+      </c>
+      <c r="M573" t="inlineStr">
         <is>
           <t>CEBADA</t>
         </is>
